--- a/data/data_quarterly.xlsx
+++ b/data/data_quarterly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\economics\GIT\monmacro\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF3E3B0-1BA8-45E3-B442-6C8FCF77EA4B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E742E171-2842-4AB9-AC3D-DFFFC829692A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>gdp_nom</t>
   </si>
@@ -630,6 +630,12 @@
   <si>
     <t>25Q3</t>
   </si>
+  <si>
+    <t>25Q4</t>
+  </si>
+  <si>
+    <t>26Q1</t>
+  </si>
 </sst>
 </file>
 
@@ -986,7 +992,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1117,15 +1123,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1183,7 +1180,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1192,18 +1189,13 @@
     <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="33" borderId="11" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="33" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="42" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="42" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1561,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CW118"/>
+  <dimension ref="A1:CW121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
@@ -21549,131 +21541,131 @@
         <v>2630693</v>
       </c>
     </row>
-    <row r="98" spans="1:101" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
+    <row r="98" spans="1:101" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="8">
         <v>16544459.6</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="8">
         <v>382951.5</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="8">
         <v>5869321.7000000002</v>
       </c>
-      <c r="E98" s="10">
+      <c r="E98" s="8">
         <v>1012844.5</v>
       </c>
-      <c r="F98" s="10">
+      <c r="F98" s="8">
         <v>420716.7</v>
       </c>
-      <c r="G98" s="10">
+      <c r="G98" s="8">
         <v>155796.4</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="8">
         <v>1395430.6</v>
       </c>
-      <c r="I98" s="10">
+      <c r="I98" s="8">
         <v>1044874.7</v>
       </c>
-      <c r="J98" s="10">
+      <c r="J98" s="8">
         <v>305838.7</v>
       </c>
-      <c r="K98" s="10">
+      <c r="K98" s="8">
         <v>4131427.2</v>
       </c>
-      <c r="L98" s="10">
+      <c r="L98" s="8">
         <v>1825257.5</v>
       </c>
-      <c r="AI98" s="10">
+      <c r="AI98" s="8">
         <v>6084179.7000000002</v>
       </c>
-      <c r="AJ98" s="10">
+      <c r="AJ98" s="8">
         <v>173284.2</v>
       </c>
-      <c r="AK98" s="10">
+      <c r="AK98" s="8">
         <v>914909.6</v>
       </c>
-      <c r="AL98" s="10">
+      <c r="AL98" s="8">
         <v>344608.9</v>
       </c>
-      <c r="AM98" s="10">
+      <c r="AM98" s="8">
         <v>264306.59999999998</v>
       </c>
-      <c r="AN98" s="10">
+      <c r="AN98" s="8">
         <v>64585.2</v>
       </c>
-      <c r="AO98" s="10">
+      <c r="AO98" s="8">
         <v>693765.9</v>
       </c>
-      <c r="AP98" s="10">
+      <c r="AP98" s="8">
         <v>324850.7</v>
       </c>
-      <c r="AQ98" s="10">
+      <c r="AQ98" s="8">
         <v>240606.1</v>
       </c>
-      <c r="AR98" s="10">
+      <c r="AR98" s="8">
         <v>2036390.5</v>
       </c>
-      <c r="AS98" s="10">
+      <c r="AS98" s="8">
         <v>1026872</v>
       </c>
-      <c r="AT98" s="9">
+      <c r="AT98" s="7">
         <v>2283.6999999999998</v>
       </c>
-      <c r="AU98" s="9">
+      <c r="AU98" s="7">
         <v>1798.7</v>
       </c>
-      <c r="AV98" s="10">
+      <c r="AV98" s="1">
         <v>2423344</v>
       </c>
-      <c r="AW98" s="10">
+      <c r="AW98" s="1">
         <v>2282131</v>
       </c>
-      <c r="AX98" s="10">
+      <c r="AX98" s="1">
         <v>1309363</v>
       </c>
-      <c r="AY98" s="10">
+      <c r="AY98" s="1">
         <v>506263</v>
       </c>
-      <c r="AZ98" s="10">
+      <c r="AZ98" s="1">
         <v>175397</v>
       </c>
-      <c r="BA98" s="10">
+      <c r="BA98" s="1">
         <v>131884</v>
       </c>
-      <c r="BB98" s="10">
+      <c r="BB98" s="1">
         <v>56074</v>
       </c>
-      <c r="BC98" s="10">
+      <c r="BC98" s="1">
         <v>85139</v>
       </c>
-      <c r="BD98" s="10">
+      <c r="BD98" s="1">
         <v>2471147</v>
       </c>
-      <c r="BE98" s="10">
+      <c r="BE98" s="1">
         <v>2329934</v>
       </c>
-      <c r="BF98" s="10">
+      <c r="BF98" s="1">
         <v>473821</v>
       </c>
-      <c r="BG98" s="10">
+      <c r="BG98" s="1">
         <v>1556441</v>
       </c>
-      <c r="BH98" s="10">
+      <c r="BH98" s="1">
         <v>45703</v>
       </c>
-      <c r="BI98" s="10">
+      <c r="BI98" s="1">
         <v>56074</v>
       </c>
-      <c r="BJ98" s="10">
+      <c r="BJ98" s="1">
         <v>85139</v>
       </c>
-      <c r="CV98" s="10">
+      <c r="CV98" s="8">
         <v>17902.2</v>
       </c>
-      <c r="CW98" s="10">
+      <c r="CW98" s="8">
         <v>1734426.8</v>
       </c>
     </row>
@@ -22003,10 +21995,10 @@
       <c r="AS101" s="1">
         <v>743905.9</v>
       </c>
-      <c r="AT101" s="6">
+      <c r="AT101" s="4">
         <v>2672</v>
       </c>
-      <c r="AU101" s="7">
+      <c r="AU101" s="5">
         <v>2229.4</v>
       </c>
       <c r="AV101" s="1">
@@ -22061,29 +22053,29 @@
         <v>2061420.2</v>
       </c>
     </row>
-    <row r="102" spans="1:101" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:101" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>200</v>
       </c>
       <c r="B102" s="1">
         <v>17400531.800000001</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="1">
         <v>547605.19999999995</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="1">
         <v>5335584.0999999996</v>
       </c>
-      <c r="E102" s="3">
+      <c r="E102" s="1">
         <v>1112696.8</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102" s="1">
         <v>524724.4</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="1">
         <v>162224.29999999999</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="1">
         <v>1413457.2</v>
       </c>
       <c r="I102" s="1">
@@ -22131,10 +22123,10 @@
       <c r="AS102" s="1">
         <v>995272.3</v>
       </c>
-      <c r="AT102" s="11">
+      <c r="AT102" s="9">
         <v>2642.3</v>
       </c>
-      <c r="AU102" s="7">
+      <c r="AU102" s="5">
         <v>2245.3000000000002</v>
       </c>
       <c r="AV102" s="1">
@@ -22183,47 +22175,47 @@
         <v>102581</v>
       </c>
       <c r="CV102" s="1">
-        <v>18270.400000000001</v>
+        <v>18412.3</v>
       </c>
       <c r="CW102" s="1">
-        <v>1178644.6000000001</v>
+        <v>1186499.5</v>
       </c>
     </row>
     <row r="103" spans="1:101" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>201</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="1">
         <v>22861788.199999999</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
         <v>4315411.3</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="1">
         <v>4963483.0999999996</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="1">
         <v>867811.3</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="1">
         <v>448851.7</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="1">
         <v>566593.80000000005</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
         <v>1743213.2</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="1">
         <v>897436.3</v>
       </c>
-      <c r="J103">
+      <c r="J103" s="1">
         <v>403002.4</v>
       </c>
-      <c r="K103">
+      <c r="K103" s="1">
         <v>6474228.9000000004</v>
       </c>
-      <c r="L103">
+      <c r="L103" s="1">
         <v>2181756.1</v>
       </c>
       <c r="AI103" s="1">
@@ -22259,10 +22251,10 @@
       <c r="AS103" s="1">
         <v>1436152.3</v>
       </c>
-      <c r="AT103" s="11">
+      <c r="AT103" s="9">
         <v>2740.7</v>
       </c>
-      <c r="AU103" s="7">
+      <c r="AU103" s="5">
         <v>2355.8000000000002</v>
       </c>
       <c r="AV103" s="1">
@@ -22311,86 +22303,86 @@
         <v>124184</v>
       </c>
       <c r="CV103" s="1">
-        <v>21951.8</v>
+        <v>22154.2</v>
       </c>
       <c r="CW103" s="1">
-        <v>1387052.3</v>
+        <v>1526016.6</v>
       </c>
     </row>
     <row r="104" spans="1:101" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>202</v>
       </c>
-      <c r="B104" s="8">
+      <c r="B104" s="1">
         <v>19861276.199999999</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="1">
         <v>2170549.81</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="1">
         <v>2842152.54</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="1">
         <v>1130169.5</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="1">
         <v>334806.18</v>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="1">
         <v>701773.14</v>
       </c>
-      <c r="H104" s="8">
+      <c r="H104" s="1">
         <v>2002933.73</v>
       </c>
-      <c r="I104" s="8">
+      <c r="I104" s="1">
         <v>1442851.03</v>
       </c>
-      <c r="J104" s="8">
+      <c r="J104" s="1">
         <v>481144.29</v>
       </c>
-      <c r="K104" s="8">
+      <c r="K104" s="1">
         <v>6819346.5700000003</v>
       </c>
-      <c r="L104" s="8">
+      <c r="L104" s="1">
         <v>1935549.43</v>
       </c>
-      <c r="AI104" s="8">
+      <c r="AI104" s="6">
         <v>8993108.0600000005</v>
       </c>
-      <c r="AJ104" s="8">
+      <c r="AJ104" s="6">
         <v>1107891.19</v>
       </c>
-      <c r="AK104" s="8">
+      <c r="AK104" s="6">
         <v>1400009.95</v>
       </c>
-      <c r="AL104" s="8">
+      <c r="AL104" s="6">
         <v>567233.11</v>
       </c>
-      <c r="AM104" s="8">
+      <c r="AM104" s="6">
         <v>157487.07</v>
       </c>
-      <c r="AN104" s="8">
+      <c r="AN104" s="6">
         <v>246023.83</v>
       </c>
-      <c r="AO104" s="8">
+      <c r="AO104" s="6">
         <v>978046.35</v>
       </c>
-      <c r="AP104" s="8">
+      <c r="AP104" s="6">
         <v>636302.93999999994</v>
       </c>
-      <c r="AQ104" s="8">
+      <c r="AQ104" s="6">
         <v>265279.34999999998</v>
       </c>
-      <c r="AR104" s="8">
+      <c r="AR104" s="6">
         <v>2509145.91</v>
       </c>
-      <c r="AS104" s="8">
+      <c r="AS104" s="6">
         <v>1125688.3700000001</v>
       </c>
-      <c r="AT104" s="11">
+      <c r="AT104" s="9">
         <v>2713.9</v>
       </c>
-      <c r="AU104" s="7">
+      <c r="AU104" s="5">
         <v>2312.1</v>
       </c>
       <c r="AV104" s="1">
@@ -22439,22 +22431,145 @@
         <v>97114</v>
       </c>
       <c r="CV104" s="1">
-        <v>26880.1</v>
+        <v>26888.3</v>
       </c>
       <c r="CW104" s="1">
-        <v>1359073.8</v>
+        <v>1440760.5</v>
       </c>
     </row>
     <row r="105" spans="1:101" x14ac:dyDescent="0.3">
-      <c r="AT105" s="11">
+      <c r="A105" t="s">
+        <v>203</v>
+      </c>
+      <c r="B105" s="1">
+        <v>29813531.5</v>
+      </c>
+      <c r="C105" s="1">
+        <v>1005763.2</v>
+      </c>
+      <c r="D105" s="1">
+        <v>9605857.9000000004</v>
+      </c>
+      <c r="E105" s="1">
+        <v>2173350.1</v>
+      </c>
+      <c r="F105" s="1">
+        <v>711609.1</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2019827</v>
+      </c>
+      <c r="H105" s="1">
+        <v>3809609</v>
+      </c>
+      <c r="I105" s="1">
+        <v>1107976</v>
+      </c>
+      <c r="J105" s="1">
+        <v>580771.9</v>
+      </c>
+      <c r="K105" s="1">
+        <v>6235692.2000000002</v>
+      </c>
+      <c r="L105" s="1">
+        <v>2563075.2000000002</v>
+      </c>
+      <c r="AI105" s="1">
+        <v>10081379.9</v>
+      </c>
+      <c r="AJ105" s="1">
+        <v>613542.1</v>
+      </c>
+      <c r="AK105" s="1">
+        <v>1447040.5</v>
+      </c>
+      <c r="AL105" s="1">
+        <v>1119335.7</v>
+      </c>
+      <c r="AM105" s="1">
+        <v>290873.2</v>
+      </c>
+      <c r="AN105" s="1">
+        <v>664823.9</v>
+      </c>
+      <c r="AO105" s="1">
+        <v>1168067.3999999999</v>
+      </c>
+      <c r="AP105" s="1">
+        <v>958150.9</v>
+      </c>
+      <c r="AQ105" s="1">
+        <v>258697.3</v>
+      </c>
+      <c r="AR105" s="1">
+        <v>2737825.1</v>
+      </c>
+      <c r="AS105" s="1">
+        <v>823023.8</v>
+      </c>
+      <c r="AT105" s="10">
         <v>2877.8</v>
       </c>
-      <c r="AU105" s="7">
+      <c r="AU105" s="1">
         <v>2482.1999999999998</v>
+      </c>
+      <c r="AV105" s="1">
+        <v>3012907</v>
+      </c>
+      <c r="AW105" s="1">
+        <v>2841561</v>
+      </c>
+      <c r="AX105" s="1">
+        <v>1632962</v>
+      </c>
+      <c r="AY105" s="1">
+        <v>603157</v>
+      </c>
+      <c r="AZ105" s="1">
+        <v>224388</v>
+      </c>
+      <c r="BA105" s="1">
+        <v>158203</v>
+      </c>
+      <c r="BB105" s="1">
+        <v>75473</v>
+      </c>
+      <c r="BC105" s="1">
+        <v>95873</v>
+      </c>
+      <c r="BD105" s="1">
+        <v>3103779</v>
+      </c>
+      <c r="BE105" s="1">
+        <v>2932433</v>
+      </c>
+      <c r="BF105" s="1">
+        <v>508436</v>
+      </c>
+      <c r="BG105" s="1">
+        <v>2039997</v>
+      </c>
+      <c r="BH105" s="1">
+        <v>62090</v>
+      </c>
+      <c r="BI105" s="1">
+        <v>75473</v>
+      </c>
+      <c r="BJ105" s="1">
+        <v>95873</v>
+      </c>
+      <c r="CV105" s="1">
+        <v>29071.599999999999</v>
+      </c>
+      <c r="CW105" s="1">
+        <v>2016357.2</v>
       </c>
     </row>
     <row r="106" spans="1:101" x14ac:dyDescent="0.3">
-      <c r="AU106" s="7"/>
+      <c r="A106" t="s">
+        <v>204</v>
+      </c>
+      <c r="AU106" s="5"/>
       <c r="AV106" s="1"/>
       <c r="AW106" s="1"/>
       <c r="AX106" s="1"/>
@@ -22487,7 +22602,7 @@
       <c r="AQ107" s="1"/>
       <c r="AR107" s="1"/>
       <c r="AS107" s="1"/>
-      <c r="AU107" s="7"/>
+      <c r="AU107" s="5"/>
       <c r="AV107" s="1"/>
       <c r="AW107" s="1"/>
       <c r="AX107" s="1"/>
@@ -22529,19 +22644,217 @@
       <c r="BB108" s="1"/>
       <c r="BC108" s="1"/>
     </row>
-    <row r="113" spans="48:101" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:101" x14ac:dyDescent="0.3">
+      <c r="AI109" s="1"/>
+      <c r="AJ109" s="1"/>
+      <c r="AK109" s="1"/>
+      <c r="AL109" s="1"/>
+      <c r="AM109" s="1"/>
+      <c r="AN109" s="1"/>
+      <c r="AO109" s="1"/>
+      <c r="AP109" s="1"/>
+      <c r="AQ109" s="1"/>
+      <c r="AR109" s="1"/>
+      <c r="AS109" s="1"/>
+    </row>
+    <row r="110" spans="1:101" x14ac:dyDescent="0.3">
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="AI110" s="1"/>
+      <c r="AJ110" s="1"/>
+      <c r="AK110" s="1"/>
+      <c r="AL110" s="1"/>
+      <c r="AM110" s="1"/>
+      <c r="AN110" s="1"/>
+      <c r="AO110" s="1"/>
+      <c r="AP110" s="1"/>
+      <c r="AQ110" s="1"/>
+      <c r="AR110" s="1"/>
+      <c r="AS110" s="1"/>
+      <c r="BD110" s="1"/>
+      <c r="BE110" s="1"/>
+      <c r="BF110" s="1"/>
+      <c r="BG110" s="1"/>
+      <c r="BH110" s="1"/>
+      <c r="BI110" s="1"/>
+      <c r="BJ110" s="1"/>
+    </row>
+    <row r="111" spans="1:101" x14ac:dyDescent="0.3">
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="AI111" s="1"/>
+      <c r="AJ111" s="1"/>
+      <c r="AK111" s="1"/>
+      <c r="AL111" s="1"/>
+      <c r="AM111" s="1"/>
+      <c r="AN111" s="1"/>
+      <c r="AO111" s="1"/>
+      <c r="AP111" s="1"/>
+      <c r="AQ111" s="1"/>
+      <c r="AR111" s="1"/>
+      <c r="AS111" s="1"/>
+      <c r="BD111" s="1"/>
+      <c r="BE111" s="1"/>
+      <c r="BF111" s="1"/>
+      <c r="BG111" s="1"/>
+      <c r="BH111" s="1"/>
+      <c r="BI111" s="1"/>
+      <c r="BJ111" s="1"/>
+    </row>
+    <row r="112" spans="1:101" x14ac:dyDescent="0.3">
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="AI112" s="1"/>
+      <c r="AJ112" s="1"/>
+      <c r="AK112" s="1"/>
+      <c r="AL112" s="1"/>
+      <c r="AM112" s="1"/>
+      <c r="AN112" s="1"/>
+      <c r="AO112" s="1"/>
+      <c r="AP112" s="1"/>
+      <c r="AQ112" s="1"/>
+      <c r="AR112" s="1"/>
+      <c r="AS112" s="1"/>
+      <c r="BD112" s="1"/>
+      <c r="BE112" s="1"/>
+      <c r="BF112" s="1"/>
+      <c r="BG112" s="1"/>
+      <c r="BH112" s="1"/>
+      <c r="BI112" s="1"/>
+      <c r="BJ112" s="1"/>
+    </row>
+    <row r="113" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="AI113" s="1"/>
+      <c r="AJ113" s="1"/>
+      <c r="AK113" s="1"/>
+      <c r="AL113" s="1"/>
+      <c r="AM113" s="1"/>
+      <c r="AN113" s="1"/>
+      <c r="AO113" s="1"/>
+      <c r="AP113" s="1"/>
+      <c r="AQ113" s="1"/>
+      <c r="AR113" s="1"/>
+      <c r="AS113" s="1"/>
+      <c r="BD113" s="1"/>
+      <c r="BE113" s="1"/>
+      <c r="BF113" s="1"/>
+      <c r="BG113" s="1"/>
+      <c r="BH113" s="1"/>
+      <c r="BI113" s="1"/>
+      <c r="BJ113" s="1"/>
+      <c r="CU113" s="1"/>
       <c r="CV113" s="1"/>
-      <c r="CW113" s="1"/>
     </row>
-    <row r="114" spans="48:101" x14ac:dyDescent="0.3">
-      <c r="CV114" s="1"/>
-      <c r="CW114" s="1"/>
+    <row r="114" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AI114" s="1"/>
+      <c r="AJ114" s="1"/>
+      <c r="AK114" s="1"/>
+      <c r="AL114" s="1"/>
+      <c r="AM114" s="1"/>
+      <c r="AN114" s="1"/>
+      <c r="AO114" s="1"/>
+      <c r="AP114" s="1"/>
+      <c r="AQ114" s="1"/>
+      <c r="AR114" s="1"/>
+      <c r="AS114" s="1"/>
+      <c r="AV114" s="1"/>
+      <c r="AW114" s="1"/>
+      <c r="AX114" s="1"/>
+      <c r="AY114" s="1"/>
+      <c r="AZ114" s="1"/>
+      <c r="BA114" s="1"/>
+      <c r="BB114" s="1"/>
+      <c r="BC114" s="1"/>
+      <c r="BD114" s="1"/>
+      <c r="BE114" s="1"/>
+      <c r="BF114" s="1"/>
+      <c r="BG114" s="1"/>
+      <c r="BH114" s="1"/>
+      <c r="BI114" s="1"/>
+      <c r="BJ114" s="1"/>
+      <c r="CT114" s="1"/>
+      <c r="CU114" s="1"/>
     </row>
-    <row r="115" spans="48:101" x14ac:dyDescent="0.3">
-      <c r="CV115" s="1"/>
-      <c r="CW115" s="1"/>
+    <row r="115" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AI115" s="1"/>
+      <c r="AJ115" s="1"/>
+      <c r="AK115" s="1"/>
+      <c r="AL115" s="1"/>
+      <c r="AM115" s="1"/>
+      <c r="AN115" s="1"/>
+      <c r="AO115" s="1"/>
+      <c r="AP115" s="1"/>
+      <c r="AQ115" s="1"/>
+      <c r="AR115" s="1"/>
+      <c r="AS115" s="1"/>
+      <c r="AV115" s="1"/>
+      <c r="AW115" s="1"/>
+      <c r="AX115" s="1"/>
+      <c r="AY115" s="1"/>
+      <c r="AZ115" s="1"/>
+      <c r="BA115" s="1"/>
+      <c r="BB115" s="1"/>
+      <c r="BC115" s="1"/>
+      <c r="BD115" s="1"/>
+      <c r="BE115" s="1"/>
+      <c r="BF115" s="1"/>
+      <c r="BG115" s="1"/>
+      <c r="BH115" s="1"/>
+      <c r="BI115" s="1"/>
+      <c r="BJ115" s="1"/>
+      <c r="CT115" s="1"/>
+      <c r="CU115" s="1"/>
     </row>
-    <row r="116" spans="48:101" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AI116" s="1"/>
+      <c r="AJ116" s="1"/>
+      <c r="AK116" s="1"/>
+      <c r="AL116" s="1"/>
+      <c r="AM116" s="1"/>
+      <c r="AN116" s="1"/>
+      <c r="AO116" s="1"/>
+      <c r="AP116" s="1"/>
+      <c r="AQ116" s="1"/>
+      <c r="AR116" s="1"/>
+      <c r="AS116" s="1"/>
       <c r="AV116" s="1"/>
       <c r="AW116" s="1"/>
       <c r="AX116" s="1"/>
@@ -22549,6 +22862,7 @@
       <c r="AZ116" s="1"/>
       <c r="BA116" s="1"/>
       <c r="BB116" s="1"/>
+      <c r="BC116" s="1"/>
       <c r="BD116" s="1"/>
       <c r="BE116" s="1"/>
       <c r="BF116" s="1"/>
@@ -22557,7 +22871,7 @@
       <c r="BI116" s="1"/>
       <c r="BJ116" s="1"/>
     </row>
-    <row r="117" spans="48:101" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:100" x14ac:dyDescent="0.3">
       <c r="AV117" s="1"/>
       <c r="AW117" s="1"/>
       <c r="AX117" s="1"/>
@@ -22565,6 +22879,7 @@
       <c r="AZ117" s="1"/>
       <c r="BA117" s="1"/>
       <c r="BB117" s="1"/>
+      <c r="BC117" s="1"/>
       <c r="BD117" s="1"/>
       <c r="BE117" s="1"/>
       <c r="BF117" s="1"/>
@@ -22573,7 +22888,7 @@
       <c r="BI117" s="1"/>
       <c r="BJ117" s="1"/>
     </row>
-    <row r="118" spans="48:101" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:100" x14ac:dyDescent="0.3">
       <c r="AV118" s="1"/>
       <c r="AW118" s="1"/>
       <c r="AX118" s="1"/>
@@ -22581,13 +22896,43 @@
       <c r="AZ118" s="1"/>
       <c r="BA118" s="1"/>
       <c r="BB118" s="1"/>
+      <c r="BC118" s="1"/>
       <c r="BD118" s="1"/>
       <c r="BE118" s="1"/>
       <c r="BF118" s="1"/>
       <c r="BG118" s="1"/>
       <c r="BH118" s="1"/>
       <c r="BI118" s="1"/>
-      <c r="BJ118" s="1"/>
+    </row>
+    <row r="119" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AV119" s="1"/>
+      <c r="AW119" s="1"/>
+      <c r="AX119" s="1"/>
+      <c r="AY119" s="1"/>
+      <c r="AZ119" s="1"/>
+      <c r="BA119" s="1"/>
+      <c r="BB119" s="1"/>
+      <c r="BC119" s="1"/>
+    </row>
+    <row r="120" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AV120" s="1"/>
+      <c r="AW120" s="1"/>
+      <c r="AX120" s="1"/>
+      <c r="AY120" s="1"/>
+      <c r="AZ120" s="1"/>
+      <c r="BA120" s="1"/>
+      <c r="BB120" s="1"/>
+      <c r="BC120" s="1"/>
+    </row>
+    <row r="121" spans="2:100" x14ac:dyDescent="0.3">
+      <c r="AV121" s="1"/>
+      <c r="AW121" s="1"/>
+      <c r="AX121" s="1"/>
+      <c r="AY121" s="1"/>
+      <c r="AZ121" s="1"/>
+      <c r="BA121" s="1"/>
+      <c r="BB121" s="1"/>
+      <c r="BC121" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
